--- a/12610356.xlsx
+++ b/12610356.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -201,6 +201,12 @@
   </si>
   <si>
     <t xml:space="preserve">Went for a morning walk, attended classes from 9 to 5, completed coding practice, and spent time talking with parents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Focused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exam preparation day; skipped the walk and gym, revised class topics, practiced coding, and called parents.</t>
   </si>
 </sst>
 </file>
@@ -1230,27 +1236,51 @@
         <v>59</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23"/>
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24"/>
-      <c r="F9" s="24"/>
-      <c r="G9" s="24"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="25" t="str">
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="18" t="n">
+        <v>46264</v>
+      </c>
+      <c r="B9" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I9" s="20" t="n">
         <f aca="false">IF(SUM(B9:F9,H9)=0,"",SUM(B9:F9,H9))</f>
-        <v/>
-      </c>
-      <c r="J9" s="25" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J9" s="20" t="n">
         <f aca="false">IF(I9="","",1440-I9)</f>
-        <v/>
-      </c>
-      <c r="K9" s="26"/>
-      <c r="L9" s="26"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="27"/>
+        <v>120</v>
+      </c>
+      <c r="K9" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M9" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N9" s="22" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23"/>

--- a/12610356.xlsx
+++ b/12610356.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -207,6 +207,15 @@
   </si>
   <si>
     <t xml:space="preserve">Exam preparation day; skipped the walk and gym, revised class topics, practiced coding, and called parents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Went to the gym after classes, reviewed notes, solved coding questions, and had a long conversation with parents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Productive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Read in the morning, did a short walk, attended all classes, and made steady progress with coding practice.</t>
   </si>
 </sst>
 </file>
@@ -1282,49 +1291,97 @@
         <v>61</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
-      <c r="I10" s="25" t="str">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B10" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C10" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="D10" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="I10" s="20" t="n">
         <f aca="false">IF(SUM(B10:F10,H10)=0,"",SUM(B10:F10,H10))</f>
-        <v/>
-      </c>
-      <c r="J10" s="25" t="str">
+        <v>1290</v>
+      </c>
+      <c r="J10" s="20" t="n">
         <f aca="false">IF(I10="","",1440-I10)</f>
-        <v/>
-      </c>
-      <c r="K10" s="26"/>
-      <c r="L10" s="26"/>
-      <c r="M10" s="26"/>
-      <c r="N10" s="27"/>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23"/>
-      <c r="B11" s="24"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="24"/>
-      <c r="I11" s="25" t="str">
+        <v>150</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="22" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="18" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B11" s="19" t="n">
+        <v>435</v>
+      </c>
+      <c r="C11" s="19" t="n">
+        <v>20</v>
+      </c>
+      <c r="D11" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I11" s="20" t="n">
         <f aca="false">IF(SUM(B11:F11,H11)=0,"",SUM(B11:F11,H11))</f>
-        <v/>
-      </c>
-      <c r="J11" s="25" t="str">
+        <v>1265</v>
+      </c>
+      <c r="J11" s="20" t="n">
         <f aca="false">IF(I11="","",1440-I11)</f>
-        <v/>
-      </c>
-      <c r="K11" s="26"/>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="27"/>
+        <v>175</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M11" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N11" s="22" t="s">
+        <v>64</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23"/>

--- a/12610356.xlsx
+++ b/12610356.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -216,6 +216,24 @@
   </si>
   <si>
     <t xml:space="preserve">Read in the morning, did a short walk, attended all classes, and made steady progress with coding practice.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tired</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Moderately Satisfied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spent extra time studying for an exam, missed the gym, revised important topics, and spoke to parents in the evening.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motivated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Morning walk and reading, full day of classes, coding practice, gym session, and around two hours talking to parents.</t>
   </si>
 </sst>
 </file>
@@ -1383,49 +1401,97 @@
         <v>64</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23"/>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-      <c r="I12" s="25" t="str">
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B12" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="C12" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="19" t="n">
+        <v>210</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>30</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="I12" s="20" t="n">
         <f aca="false">IF(SUM(B12:F12,H12)=0,"",SUM(B12:F12,H12))</f>
-        <v/>
-      </c>
-      <c r="J12" s="25" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J12" s="20" t="n">
         <f aca="false">IF(I12="","",1440-I12)</f>
-        <v/>
-      </c>
-      <c r="K12" s="26"/>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="27"/>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23"/>
-      <c r="B13" s="24"/>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-      <c r="I13" s="25" t="str">
+        <v>180</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>66</v>
+      </c>
+      <c r="M12" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="N12" s="22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="18" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B13" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C13" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="D13" s="19" t="n">
+        <v>120</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <f aca="false">IF(SUM(B13:F13,H13)=0,"",SUM(B13:F13,H13))</f>
-        <v/>
-      </c>
-      <c r="J13" s="25" t="str">
+        <v>1320</v>
+      </c>
+      <c r="J13" s="20" t="n">
         <f aca="false">IF(I13="","",1440-I13)</f>
-        <v/>
-      </c>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="27"/>
+        <v>120</v>
+      </c>
+      <c r="K13" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M13" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="22" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23"/>

--- a/12610356.xlsx
+++ b/12610356.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t xml:space="preserve">Morning walk and reading, full day of classes, coding practice, gym session, and around two hours talking to parents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stayed in to prepare for an upcoming test, practiced more coding questions than usual, and caught up with parents.</t>
   </si>
 </sst>
 </file>
@@ -1493,27 +1496,51 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="23"/>
-      <c r="B14" s="24"/>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-      <c r="I14" s="25" t="str">
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="18" t="n">
+        <v>46269</v>
+      </c>
+      <c r="B14" s="19" t="n">
+        <v>435</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <v>150</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H14" s="19" t="n">
+        <v>165</v>
+      </c>
+      <c r="I14" s="20" t="n">
         <f aca="false">IF(SUM(B14:F14,H14)=0,"",SUM(B14:F14,H14))</f>
-        <v/>
-      </c>
-      <c r="J14" s="25" t="str">
+        <v>1305</v>
+      </c>
+      <c r="J14" s="20" t="n">
         <f aca="false">IF(I14="","",1440-I14)</f>
-        <v/>
-      </c>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="27"/>
+        <v>135</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="M14" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N14" s="22" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23"/>

--- a/12610356.xlsx
+++ b/12610356.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -237,6 +237,12 @@
   </si>
   <si>
     <t xml:space="preserve">Stayed in to prepare for an upcoming test, practiced more coding questions than usual, and caught up with parents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Happy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freshened up early, attended classes, went to the gym, worked on coding consistency, and talked with parents.</t>
   </si>
 </sst>
 </file>
@@ -1542,27 +1548,51 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="23"/>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-      <c r="I15" s="25" t="str">
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="18" t="n">
+        <v>46270</v>
+      </c>
+      <c r="B15" s="19" t="n">
+        <v>420</v>
+      </c>
+      <c r="C15" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="D15" s="19" t="n">
+        <v>90</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>480</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="H15" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="I15" s="20" t="n">
         <f aca="false">IF(SUM(B15:F15,H15)=0,"",SUM(B15:F15,H15))</f>
-        <v/>
-      </c>
-      <c r="J15" s="25" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J15" s="20" t="n">
         <f aca="false">IF(I15="","",1440-I15)</f>
-        <v/>
-      </c>
-      <c r="K15" s="26"/>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="27"/>
+        <v>140</v>
+      </c>
+      <c r="K15" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="L15" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="22" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23"/>

--- a/12610356.xlsx
+++ b/12610356.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="76">
   <si>
     <t xml:space="preserve">My Data, My Code</t>
   </si>
@@ -243,6 +243,12 @@
   </si>
   <si>
     <t xml:space="preserve">Freshened up early, attended classes, went to the gym, worked on coding consistency, and talked with parents.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accomplished</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shorter class day; studied for an exam, went for a brief walk, practiced coding, and spent time with parents.</t>
   </si>
 </sst>
 </file>
@@ -1594,27 +1600,51 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="23"/>
-      <c r="B16" s="24"/>
-      <c r="C16" s="24"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="24"/>
-      <c r="F16" s="24"/>
-      <c r="G16" s="24"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="25" t="str">
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="18" t="n">
+        <v>46271</v>
+      </c>
+      <c r="B16" s="19" t="n">
+        <v>450</v>
+      </c>
+      <c r="C16" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>75</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>360</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>4</v>
+      </c>
+      <c r="H16" s="19" t="n">
+        <v>180</v>
+      </c>
+      <c r="I16" s="20" t="n">
         <f aca="false">IF(SUM(B16:F16,H16)=0,"",SUM(B16:F16,H16))</f>
-        <v/>
-      </c>
-      <c r="J16" s="25" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J16" s="20" t="n">
         <f aca="false">IF(I16="","",1440-I16)</f>
-        <v/>
-      </c>
-      <c r="K16" s="26"/>
-      <c r="L16" s="26"/>
-      <c r="M16" s="26"/>
-      <c r="N16" s="27"/>
+        <v>170</v>
+      </c>
+      <c r="K16" s="21" t="s">
+        <v>74</v>
+      </c>
+      <c r="L16" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="N16" s="22" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23"/>
